--- a/tools/precos/planilhas/precos-oficiais-numbuzin.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-numbuzin.xlsx
@@ -41,12 +41,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F4E8"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -72,7 +77,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -81,6 +86,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -582,7 +588,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -637,7 +643,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -692,7 +698,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -729,12 +735,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MB000958</t>
+          <t>MB000957</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>No.9 NAD+ Early 20s Set: essência firmadora + creme para olhos com retinal</t>
+          <t>No.9 NAD+ Glow Boosting Set: tônico com PDRN + essência firmadora</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,24 +749,24 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>316.9</v>
+        <v>319.9</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Provável — conferir</t>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No.9 NAD+ Early 20s Anti-Aging Set</t>
+          <t>No.9 NAD+ Glow Boosting Set</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" s="4" t="n">
-        <v>43.5</v>
+        <v>42</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -769,7 +775,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-9-nad-daily-glow-basic-duo</t>
+          <t>https://numbuzinus.com/products/no-9-nad-glow-boosting-set</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -784,12 +790,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MB000957</t>
+          <t>MB000958</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No.9 NAD+ Glow Boosting Set: tônico com PDRN + essência firmadora</t>
+          <t>No.9 NAD+ Early 20s Set: essência firmadora + creme para olhos com retinal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -798,24 +804,24 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>319.9</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+        <v>316.9</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No.9 NAD+ Glow Boosting Set</t>
+          <t>No.9 NAD+ Early 20s Anti-Aging Set</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" s="4" t="n">
-        <v>42</v>
+        <v>43.5</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -824,7 +830,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-9-nad-glow-boosting-set</t>
+          <t>https://numbuzinus.com/products/no-9-nad-daily-glow-basic-duo</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -855,7 +861,7 @@
       <c r="D7" s="2" t="n">
         <v>152.9</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -910,7 +916,7 @@
       <c r="D8" s="2" t="n">
         <v>80.90000000000001</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -965,7 +971,7 @@
       <c r="D9" s="2" t="n">
         <v>152.9</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Fraco — conferir</t>
         </is>
@@ -4306,7 +4312,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://numbuzinus.com · loja "numbuzin" · moeda USD · lido em 30/10/2026 06:02 UTC</t>
+          <t>Site oficial: https://numbuzinus.com · loja "numbuzin" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-numbuzin.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-numbuzin.xlsx
@@ -165,8 +165,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comparacao" displayName="Comparacao" ref="A1:N31" headerRowCount="1">
-  <autoFilter ref="A1:N31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Comparacao" displayName="Comparacao" ref="A1:N94" headerRowCount="1">
+  <autoFilter ref="A1:N94"/>
   <tableColumns count="14">
     <tableColumn id="1" name="SKU"/>
     <tableColumn id="2" name="Nosso produto"/>
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -570,12 +570,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MB001009</t>
+          <t>MB001016</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>No.1 Easy Peasy Cleansing Oil: óleo de limpeza leve 200 ml</t>
+          <t>All-in-One Masks Pack: máscaras em folha No.1 a No.5, 24 unidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>116.9</v>
+        <v>381.9</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -593,15 +593,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No.1 Easy Peasy Cleansing Oil</t>
+          <t>All-in-One Masks Pack (No.1-5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="4" t="n">
-        <v>19.5</v>
+        <v>52.5</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-1-easy-peasy-cleansing-oil-1</t>
+          <t>https://numbuzinus.com/products/count-on-masks-set-no-1-5</t>
         </is>
       </c>
       <c r="L2" s="2">
@@ -625,12 +625,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MB000983</t>
+          <t>MB001015</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>No.3 Tingle-Pore Softening Sheet Mask: máscara para poros e textura, 5 folhas</t>
+          <t>Build Your Routine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>999.99</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -648,16 +648,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No.3 Tingle-Pore Softening Sheet Mask (5 Sheets)</t>
+          <t>Build Your Routine</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>15</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="I3" s="4" t="n"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -665,7 +663,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-3-tingle-pore-softening-sheet-mask-5-sheets</t>
+          <t>https://numbuzinus.com/products/bundle-save-30</t>
         </is>
       </c>
       <c r="L3" s="2">
@@ -680,12 +678,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MB000968</t>
+          <t>MB001012</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>No.5+ Glutathione Vitamin Dark Spot Cream: creme uniformizador de glutationa 50 ml</t>
+          <t>Mini Serums Travel Set: 3 mini kits de sérum, 30 sachês</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -694,7 +692,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>162.9</v>
+        <v>217.9</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -703,15 +701,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No.5+ Glutathione Vitamin Dark Spot Cream</t>
+          <t>Mini Serums Travel Set</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" s="4" t="n">
-        <v>22.4</v>
+        <v>29.97</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -720,7 +718,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-5-glutathione-vitamin-dark-spot-cream</t>
+          <t>https://numbuzinus.com/products/mini-serums-travel-set</t>
         </is>
       </c>
       <c r="L4" s="2">
@@ -735,12 +733,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MB000957</t>
+          <t>MB001011</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>No.9 NAD+ Glow Boosting Set: tônico com PDRN + essência firmadora</t>
+          <t>No.1 Balancing Clear Skin Duo: tônico calmante de ervas + creme com vitamina B5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -749,7 +747,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>319.9</v>
+        <v>283.9</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -758,15 +756,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No.9 NAD+ Glow Boosting Set</t>
+          <t>No.1 Balancing Clear Skin Duo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" s="4" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -775,7 +773,7 @@
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-9-nad-glow-boosting-set</t>
+          <t>https://numbuzinus.com/products/no-1-breakout-free-clear-skin-duo-1</t>
         </is>
       </c>
       <c r="L5" s="2">
@@ -790,12 +788,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MB000958</t>
+          <t>MB001010</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No.9 NAD+ Early 20s Set: essência firmadora + creme para olhos com retinal</t>
+          <t>No.1 Centella Re-Leaf Green Toner Pads: discos calmantes de centella, 70 unidades</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -804,24 +802,24 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>316.9</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Provável — conferir</t>
+        <v>133.9</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No.9 NAD+ Early 20s Anti-Aging Set</t>
+          <t>No.1 Centella Re-Leaf Green Toner Pads</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" s="4" t="n">
-        <v>43.5</v>
+        <v>18</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -830,7 +828,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-9-nad-daily-glow-basic-duo</t>
+          <t>https://numbuzinus.com/products/no-1-centella-re-leaf-green-toner-pads</t>
         </is>
       </c>
       <c r="L6" s="2">
@@ -845,12 +843,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MB003179</t>
+          <t>MB001001</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2 Sérum de Colágeno PDRN 2X Rosa 30ml</t>
+          <t>No.1 Daily Calming &amp; Clear Trio: discos + sérum + máscara calmantes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -859,24 +857,24 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>336.9</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No.2 Rose PDRN Collagen 2X Plumping Serum</t>
+          <t>No.1 Daily Calming &amp; Clear Trio</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" s="4" t="n">
-        <v>19.6</v>
+        <v>46.23</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -885,7 +883,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-2-rose-pdrn-collagen-2x-plumping-serum</t>
+          <t>https://numbuzinus.com/products/no-1-sos-clear-skin-rescue-trio</t>
         </is>
       </c>
       <c r="L7" s="2">
@@ -900,12 +898,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MB003182</t>
+          <t>MB001009</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deep Cleansing Creamy Facial Foam #2, 120ml</t>
+          <t>No.1 Easy Peasy Cleansing Oil: óleo de limpeza leve 200 ml</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -914,24 +912,24 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>116.9</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No.2 Deep Clean Fresh Cream Cleansing Foam</t>
+          <t>No.1 Easy Peasy Cleansing Oil</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" s="4" t="n">
-        <v>11</v>
+        <v>19.5</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -940,7 +938,7 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-2-deep-clean-fresh-cream-cleansing-foam</t>
+          <t>https://numbuzinus.com/products/no-1-easy-peasy-cleansing-oil-1</t>
         </is>
       </c>
       <c r="L8" s="2">
@@ -955,12 +953,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MB003180</t>
+          <t>MB001008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sérum para Máscara Facial No. 6 Deep Sleep 50ml</t>
+          <t>No.1 Hydration Calming Duo: discos de centella + sérum com vitamina B5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -969,24 +967,24 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>Fraco — conferir</t>
+        <v>272.9</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No.6 Deep Sleep Mask Serum</t>
+          <t>No.1 Hydration Calming Duo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" s="4" t="n">
-        <v>21</v>
+        <v>37.44</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -995,7 +993,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-6-deep-sleep-mask-serum-1</t>
+          <t>https://numbuzinus.com/products/no-1-hydration-calming-duo</t>
         </is>
       </c>
       <c r="L9" s="2">
@@ -1010,12 +1008,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MB003189</t>
+          <t>MB001007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1 Almofadas de Cica Calmantes – 70 Almofadas</t>
+          <t>No.1 Pantothenic B5 Active Drying Powder: pó secativo com vitamina B5 7 g</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1024,27 +1022,51 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>67.89</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n"/>
+        <v>79.90000000000001</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>No.1 Pantothenic B5 Active Drying Powder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>11</v>
+      </c>
       <c r="I10" s="4" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="6" t="n"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-1-pantothenic-b5-active-drying-powder</t>
+        </is>
+      </c>
+      <c r="L10" s="2">
+        <f>ROUND(H10*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M10" s="6">
+        <f>IF(OR(D10="",L10=""),"",D10/L10-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MB003174</t>
+          <t>MB001006</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1 Discos Calmantes de Cica – 70 Discos</t>
+          <t>No.1 Pantothenic B5 Active Soothing Cream: creme calmante com vitamina B5 80 ml</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,27 +1075,53 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>67.89</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="6" t="n"/>
+        <v>182.9</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>No.1 Pantothenic B5 Active Soothing Cream</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" s="4" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-1-pantothenic-b5-active-soothing-cream</t>
+        </is>
+      </c>
+      <c r="L11" s="2">
+        <f>ROUND(H11*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M11" s="6">
+        <f>IF(OR(D11="",L11=""),"",D11/L11-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MB003176</t>
+          <t>MB001005</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2 Sérum Preenchedor com PDRN de Rosa e Colágeno – 30 ml</t>
+          <t>No.1 Pantothenic B5 Active Soothing Serum: sérum calmante com vitamina B5 50 ml</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1082,27 +1130,51 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>141.9</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n"/>
+        <v>110.9</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>No.1 Pantothenic B5 Active Soothing Serum</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>28</v>
+      </c>
       <c r="I12" s="4" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="6" t="n"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-1-pantothenic-b5-active-soothing-serum</t>
+        </is>
+      </c>
+      <c r="L12" s="2">
+        <f>ROUND(H12*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M12" s="6">
+        <f>IF(OR(D12="",L12=""),"",D12/L12-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MB003177</t>
+          <t>MB001004</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3 Ampola Remodeladora de Poros com Biorretinol Azul – 30 ml</t>
+          <t>No.1 Pantothenic B5 Hyaluronic Active Clear Mask: máscara calmante, 4 folhas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1111,27 +1183,53 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>153.9</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="6" t="n"/>
+        <v>97.90000000000001</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>No.1 Pantothenic B5 Hyaluronic Active Clear Mask (4 Sheets)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-1-pantothenic-b5-hyaluronic-active-clear-mask</t>
+        </is>
+      </c>
+      <c r="L13" s="2">
+        <f>ROUND(H13*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M13" s="6">
+        <f>IF(OR(D13="",L13=""),"",D13/L13-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MB003175</t>
+          <t>MB001003</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4 Sérum Ceraphyl Efeito "Pele de Ovo" – 30 ml</t>
+          <t>No.1 Pantothenic Skincare 100 Powder: pó matificante com vitamina B5 7 g</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1140,27 +1238,53 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>78.33</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="6" t="n"/>
+        <v>130.9</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>No.1 Pantothenic Skincare 100 Powder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-1-pantothenic-skincare-100-powder</t>
+        </is>
+      </c>
+      <c r="L14" s="2">
+        <f>ROUND(H14*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M14" s="6">
+        <f>IF(OR(D14="",L14=""),"",D14/L14-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MB003171</t>
+          <t>MB001002</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5 Adesivos de Glutationa C para Marcas e Manchas – 70 Unidades</t>
+          <t>No.1 Pure-Full Calming Herb Toner: tônico calmante de ervas 300 ml</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1169,27 +1293,53 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>68.23999999999999</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="6" t="n"/>
+        <v>136.9</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>No.1 Pure-Full Calming Herb Toner</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" s="4" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-1-pure-full-calming-herb-toner</t>
+        </is>
+      </c>
+      <c r="L15" s="2">
+        <f>ROUND(H15*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M15" s="6">
+        <f>IF(OR(D15="",L15=""),"",D15/L15-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MB003192</t>
+          <t>MB000999</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5 Ampoules Glutathione C for Marks and Spots – 30 ml</t>
+          <t>No.2 Deep Clean Fresh Cream Cleansing Foam: espuma cremosa de limpeza 120 ml</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1198,27 +1348,53 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>73.11</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="6" t="n"/>
+        <v>79.90000000000001</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>No.2 Deep Clean Fresh Cream Cleansing Foam</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-2-deep-clean-fresh-cream-cleansing-foam</t>
+        </is>
+      </c>
+      <c r="L16" s="2">
+        <f>ROUND(H16*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M16" s="6">
+        <f>IF(OR(D16="",L16=""),"",D16/L16-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MB003190</t>
+          <t>MB000998</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5 Máscara Facial em Filme com Glutationa e Vitamina C – 5 Unidades</t>
+          <t>No.2 Rose PDRN Collagen 2X Plumping Serum: sérum preenchedor com PDRN 30 ml</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1227,27 +1403,53 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>109.9</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="6" t="n"/>
+        <v>152.9</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>No.2 Rose PDRN Collagen 2X Plumping Serum</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" s="4" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-2-rose-pdrn-collagen-2x-plumping-serum</t>
+        </is>
+      </c>
+      <c r="L17" s="2">
+        <f>ROUND(H17*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M17" s="6">
+        <f>IF(OR(D17="",L17=""),"",D17/L17-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MB003193</t>
+          <t>MB000996</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Discos de Tônico, 2 tipos, 1+1 (140 discos)</t>
+          <t>No.2 Rose PDRN Collagen Plumping Sheet Mask: máscara de colágeno, 5 folhas</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1256,27 +1458,53 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>279.9</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="6" t="n"/>
+        <v>97.90000000000001</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>No.2 Rose PDRN Collagen Plumping Sheet Mask (5 Sheets)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-2-rose-pdrn-collagen-plumping-sheet-mask-5-sheets</t>
+        </is>
+      </c>
+      <c r="L18" s="2">
+        <f>ROUND(H18*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M18" s="6">
+        <f>IF(OR(D18="",L18=""),"",D18/L18-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MB003181</t>
+          <t>MB001000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Essential Tonic Vita-Glutathione C Supplement No. 5 200ml</t>
+          <t>No.2 e 2X Rose PDRN Collagen Plumping Serum: mini kit 10 sachês de 1,2 ml</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1285,27 +1513,53 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>62.67</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="6" t="n"/>
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>No.2 &amp; 2X Rose PDRN Collagen Plumping Serum Mini Kit (10EA)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" s="4" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-2-rose-pdrn-collagen-plumping-serum-duo</t>
+        </is>
+      </c>
+      <c r="L19" s="2">
+        <f>ROUND(H19*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M19" s="6">
+        <f>IF(OR(D19="",L19=""),"",D19/L19-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MB003194</t>
+          <t>MB000994</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kit de Máscaras 1+1, 6 tipos (10 unidades)</t>
+          <t>No.3 Bifida Bakuchiol Exfoliating Toner Pads: discos esfoliantes, 70 unidades</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1314,27 +1568,53 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>214.9</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="L20" s="2" t="n"/>
-      <c r="M20" s="6" t="n"/>
+        <v>133.9</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>No.3 Bifida Bakuchiol Exfoliating Toner Pads</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" s="4" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-bifida-bakuchiol-exfoliating-toner-pads</t>
+        </is>
+      </c>
+      <c r="L20" s="2">
+        <f>ROUND(H20*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M20" s="6">
+        <f>IF(OR(D20="",L20=""),"",D20/L20-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MB003178</t>
+          <t>MB000993</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Máscara Facial de Colágeno PDRN Rosa nº 2 (5 unidades)</t>
+          <t>No.3 Bifida Bakuchiol Zero Pore Cleansing Oil: óleo de limpeza para poros 200 ml</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1343,27 +1623,53 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="6" t="n"/>
+        <v>116.9</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>No.3 Bifida Bakuchiol Zero Pore Cleansing Oil</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" s="4" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-bifida-bakuchiol-zero-pore-cleansing-oil</t>
+        </is>
+      </c>
+      <c r="L21" s="2">
+        <f>ROUND(H21*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M21" s="6">
+        <f>IF(OR(D21="",L21=""),"",D21/L21-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MB003172</t>
+          <t>MB000992</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>No.3 PHA Prep Bubble Pack: espuma de bolhas com PHA para textura 90 ml</t>
+          <t>No.3 Bifida Bakuchiol Zero Pore Milky Moisturizer: hidratante leitoso 150 ml</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1372,27 +1678,53 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>144.9</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="L22" s="2" t="n"/>
-      <c r="M22" s="6" t="n"/>
+        <v>127.9</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No.3 Bifida Bakuchiol Zero Pore Milky Moisturizer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" s="4" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-bifida-bakuchiol-zero-pore-milky-moisturizer</t>
+        </is>
+      </c>
+      <c r="L22" s="2">
+        <f>ROUND(H22*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M22" s="6">
+        <f>IF(OR(D22="",L22=""),"",D22/L22-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MB003173</t>
+          <t>MB000991</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pads de Maquiagem Sem Poros nº 3 - 70 unidades</t>
+          <t>No.3 Bifida Bakuchiol Zero Pore Milky Toner Light: tônico leitoso suave 200 ml</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1401,27 +1733,53 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>81.47</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="6" t="n"/>
+        <v>127.9</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>No.3 Bifida Bakuchiol Zero Pore Milky Toner Light</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" s="4" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-bifida-bakuchiol-zero-pore-milky-toner-light-6-76-fl-oz</t>
+        </is>
+      </c>
+      <c r="L23" s="2">
+        <f>ROUND(H23*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M23" s="6">
+        <f>IF(OR(D23="",L23=""),"",D23/L23-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MB003220</t>
+          <t>MB000989</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Shampoo Sérum Perfect Magic Straight 530 ml</t>
+          <t>No.3 Blue Bio-Retinol Pore Refining Serum: mini kit 10 sachês de 1,3 ml</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1430,27 +1788,53 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>44.92</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="6" t="n"/>
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>No.3 Blue Bio-Retinol Pore Refining Serum Mini Kit (1.3ml*10EA)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" s="4" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-blue-bio-retinol-pore-refining-serum-1-3ml-10ea</t>
+        </is>
+      </c>
+      <c r="L24" s="2">
+        <f>ROUND(H24*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M24" s="6">
+        <f>IF(OR(D24="",L24=""),"",D24/L24-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MB003185</t>
+          <t>MB000990</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tônico Calmante e Purificante para Pele Clara – 300 ml</t>
+          <t>No.3 Blue Bio-Retinol Pore Refining Serum: sérum de retinol para poros 30 ml</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1459,27 +1843,53 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>137.9</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="L25" s="2" t="n"/>
-      <c r="M25" s="6" t="n"/>
+        <v>152.9</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>No.3 Blue Bio-Retinol Pore Refining Serum</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-blue-bio-retinol-pore-refining-serum</t>
+        </is>
+      </c>
+      <c r="L25" s="2">
+        <f>ROUND(H25*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M25" s="6">
+        <f>IF(OR(D25="",L25=""),"",D25/L25-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MB003188</t>
+          <t>MB000987</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tônico Intensificador para Preparação da Pele – 200 ml</t>
+          <t>No.3 Radiance Glowing Jumbo Essence Pads: discos grandes de essência para viço</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1488,27 +1898,53 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>120.9</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="L26" s="2" t="n"/>
-      <c r="M26" s="6" t="n"/>
+        <v>93.90000000000001</v>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>No.3 Radiance Glowing Jumbo Essence Pads</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-radiance-glowing-jumbo-essence-pads</t>
+        </is>
+      </c>
+      <c r="L26" s="2">
+        <f>ROUND(H26*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M26" s="6">
+        <f>IF(OR(D26="",L26=""),"",D26/L26-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MB003187</t>
+          <t>MB000986</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tônico de Tratamento Glow com NMN e PDRN – 150 ml</t>
+          <t>No.3 Rice Enzyme Skin Softening Cleansing Foam: espuma esfoliante de arroz 170 ml</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1517,27 +1953,53 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>123.9</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="L27" s="2" t="n"/>
-      <c r="M27" s="6" t="n"/>
+        <v>93.90000000000001</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>No.3 Rice Enzyme Skin Softening Cleansing Foam</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-rice-enzyme-skin-softening-cleansing-foam</t>
+        </is>
+      </c>
+      <c r="L27" s="2">
+        <f>ROUND(H27*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M27" s="6">
+        <f>IF(OR(D27="",L27=""),"",D27/L27-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MB003191</t>
+          <t>MB000984</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>numbuzin No.1 Cheongcho FPS 50+ PA++++: dupla de protetor solar calmante 2 x 50 ml</t>
+          <t>No.3 Super Glowing Essence Toner: tônico essência com fermentados 300 ml</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1546,27 +2008,53 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>279.9</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="6" t="n"/>
+        <v>172.9</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>No.3 Super Glowing Essence Toner</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" s="4" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-super-glowing-essence-toner-10-14-fl-oz-300ml</t>
+        </is>
+      </c>
+      <c r="L28" s="2">
+        <f>ROUND(H28*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M28" s="6">
+        <f>IF(OR(D28="",L28=""),"",D28/L28-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MB003184</t>
+          <t>MB000983</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>numbuzin No.1 Cheongcho FPS 50+ PA++++: protetor solar calmante com filme de água 50 ml</t>
+          <t>No.3 Tingle-Pore Softening Sheet Mask: máscara para poros e textura, 5 folhas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1575,27 +2063,53 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>139.9</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="L29" s="2" t="n"/>
-      <c r="M29" s="6" t="n"/>
+        <v>97.90000000000001</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>No.3 Tingle-Pore Softening Sheet Mask (5 Sheets)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-tingle-pore-softening-sheet-mask-5-sheets</t>
+        </is>
+      </c>
+      <c r="L29" s="2">
+        <f>ROUND(H29*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M29" s="6">
+        <f>IF(OR(D29="",L29=""),"",D29/L29-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MB003183</t>
+          <t>MB000981</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>numbuzin No.3 Porcelana Tone-up Beige FPS 50+ PA++++: protetor solar com cor 50 ml</t>
+          <t>No.4 Ceramide AHA Glazed Skin Prep Serum: mini kit 10 sachês de 1,3 ml</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1604,46 +2118,2911 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>139.9</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="6" t="n"/>
+        <v>71.90000000000001</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>No.4 Ceramide AHA Glazed Skin Prep Serum Mini Kit (1.3ml*10EA)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" s="4" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-4-ceramide-aha-glazed-skin-prep-serum-1-3ml-10ea</t>
+        </is>
+      </c>
+      <c r="L30" s="2">
+        <f>ROUND(H30*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M30" s="6">
+        <f>IF(OR(D30="",L30=""),"",D30/L30-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>MB000982</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>No.4 Ceramide AHA Glazed Skin Prep Serum: sérum esfoliante com AHA e ceramidas 30 ml</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>No.4 Ceramide AHA Glazed Skin Prep Serum</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" s="4" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-4-ceramide-aha-glazed-skin-prep-serum</t>
+        </is>
+      </c>
+      <c r="L31" s="2">
+        <f>ROUND(H31*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M31" s="6">
+        <f>IF(OR(D31="",L31=""),"",D31/L31-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MB000980</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>No.4 Hydrating Glow Mineral Toner: tônico mineral hidratante 200 ml</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>No.4 Hydrating Glow Mineral Toner</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-4-hydrating-glow-mineral-toner</t>
+        </is>
+      </c>
+      <c r="L32" s="2">
+        <f>ROUND(H32*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M32" s="6">
+        <f>IF(OR(D32="",L32=""),"",D32/L32-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MB000979</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>No.4 Icy Soothing Sheet Mask: máscara refrescante calmante, 5 folhas</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>No.4 Icy Soothing Sheet Mask (5 Sheets)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" s="4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-4-icy-soothing-sheet-mask-5-sheets</t>
+        </is>
+      </c>
+      <c r="L33" s="2">
+        <f>ROUND(H33*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M33" s="6">
+        <f>IF(OR(D33="",L33=""),"",D33/L33-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MB000978</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>No.4 Pore Zero Peeled Egg Toner Pads: discos tônicos para poros</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>No.4 Pore Zero Peeled Egg Toner Pads</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-4-pore-zero-peeled-egg-toner-pads</t>
+        </is>
+      </c>
+      <c r="L34" s="2">
+        <f>ROUND(H34*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M34" s="6">
+        <f>IF(OR(D34="",L34=""),"",D34/L34-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MB000977</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>No.5 Dark Spot Brightening Routine: rotina de 5 passos com glutationa</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>626.9</v>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>No.5 Dark Spot Brightening Routine (5 items)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-5-dark-spot-brightening-routine-5-items</t>
+        </is>
+      </c>
+      <c r="L35" s="2">
+        <f>ROUND(H35*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M35" s="6">
+        <f>IF(OR(D35="",L35=""),"",D35/L35-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MB000974</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>No.5 Spot-Fading Duo: sérum de glutationa + discos de vitaminas</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>283.9</v>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>No.5 Spot-Fading Duo</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/dark-spots-power-combo</t>
+        </is>
+      </c>
+      <c r="L36" s="2">
+        <f>ROUND(H36*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M36" s="6">
+        <f>IF(OR(D36="",L36=""),"",D36/L36-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MB000973</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>No.5 Ultimate Brightening Trio: tônico + sérum + máscara com glutationa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>343.9</v>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>No.5 Ultimate Brightening Trio</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" s="4" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-5-ultimate-brightening-trio</t>
+        </is>
+      </c>
+      <c r="L37" s="2">
+        <f>ROUND(H37*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M37" s="6">
+        <f>IF(OR(D37="",L37=""),"",D37/L37-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MB000972</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>No.5 Vitamin Boosting Essential Toner: tônico de glutationa e vitaminas 200 ml</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>119.9</v>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>No.5 Vitamin Boosting Essential Toner</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-5-vitamin-boosting-essential-toner</t>
+        </is>
+      </c>
+      <c r="L38" s="2">
+        <f>ROUND(H38*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M38" s="6">
+        <f>IF(OR(D38="",L38=""),"",D38/L38-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MB000971</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>No.5 Vitamin-Niacinamide Concentrated Toner Pads: discos de vitaminas, 70 unidades</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>No.5 Vitamin-Niacinamide Concentrated Toner Pads</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-5-vitamin-niacinamide-concentrated-toner-pads</t>
+        </is>
+      </c>
+      <c r="L39" s="2">
+        <f>ROUND(H39*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M39" s="6">
+        <f>IF(OR(D39="",L39=""),"",D39/L39-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MB000970</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>No.5+ Glutathione Vitamin Concentrated Serum: sérum de glutationa e vitaminas 30 ml</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>No.5+ Glutathione Vitamin Concentrated Serum</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-5-vitamin-concentrated-serum</t>
+        </is>
+      </c>
+      <c r="L40" s="2">
+        <f>ROUND(H40*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M40" s="6">
+        <f>IF(OR(D40="",L40=""),"",D40/L40-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MB000969</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>No.5+ Glutathione Vitamin Concentrated Sheet Mask: máscara de vitamina C, 5 folhas</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>No.5+ Glutathione Vitamin Concentrated Sheet Mask (5 Sheets)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-5-vitamin-spotlight-sheet-mask-5-sheets</t>
+        </is>
+      </c>
+      <c r="L41" s="2">
+        <f>ROUND(H41*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M41" s="6">
+        <f>IF(OR(D41="",L41=""),"",D41/L41-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MB000968</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>No.5+ Glutathione Vitamin Dark Spot Cream: creme uniformizador de glutationa 50 ml</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>No.5+ Glutathione Vitamin Dark Spot Cream</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" s="4" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-5-glutathione-vitamin-dark-spot-cream</t>
+        </is>
+      </c>
+      <c r="L42" s="2">
+        <f>ROUND(H42*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M42" s="6">
+        <f>IF(OR(D42="",L42=""),"",D42/L42-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MB000967</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>No.5+ Glutathione Vitamin Facial Spa Cleanser: óleo de limpeza com glutationa 200 ml</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>No.5+ Glutathione Vitamin Facial Spa Cleanser</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" s="4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Esgotado</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-5-glutathione-c-facial-spa-cleansing-oil</t>
+        </is>
+      </c>
+      <c r="L43" s="2">
+        <f>ROUND(H43*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M43" s="6">
+        <f>IF(OR(D43="",L43=""),"",D43/L43-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MB000966</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>No.6 Deep Sleep Mask Serum: sérum hidratante efeito máscara 50 ml</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>No.6 Deep Sleep Mask Serum</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-6-deep-sleep-mask-serum-1</t>
+        </is>
+      </c>
+      <c r="L44" s="2">
+        <f>ROUND(H44*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M44" s="6">
+        <f>IF(OR(D44="",L44=""),"",D44/L44-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MB000964</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>No.9 Advanced NAD+ Longevity Set: tônico + essência + creme para olhos com retinal</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>436.9</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>No.9 Advanced NAD+ Longevity Set</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-nad-everyday-starter-trio</t>
+        </is>
+      </c>
+      <c r="L45" s="2">
+        <f>ROUND(H45*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M45" s="6">
+        <f>IF(OR(D45="",L45=""),"",D45/L45-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MB000961</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ BIO Lifting-sil Essence: essência firmadora com NAD+ e peptídeos 50 ml</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>133.9</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ BIO Lifting-sil Essence</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-nad-bio-lifting-sil-essence</t>
+        </is>
+      </c>
+      <c r="L46" s="2">
+        <f>ROUND(H46*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M46" s="6">
+        <f>IF(OR(D46="",L46=""),"",D46/L46-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MB000959</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ Collagen Under Eye Patches: adesivos de colágeno para olhos, 5 pares</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>117.9</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ Collagen Under Eye Patches (5 Pairs)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" s="4" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-nad-collagen-under-eye-patches-5ea</t>
+        </is>
+      </c>
+      <c r="L47" s="2">
+        <f>ROUND(H47*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M47" s="6">
+        <f>IF(OR(D47="",L47=""),"",D47/L47-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MB000957</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ Glow Boosting Set: tônico com PDRN + essência firmadora</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ Glow Boosting Set</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-nad-glow-boosting-set</t>
+        </is>
+      </c>
+      <c r="L48" s="2">
+        <f>ROUND(H48*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M48" s="6">
+        <f>IF(OR(D48="",L48=""),"",D48/L48-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MB000956</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ PDRN Glow Boosting Toner: tônico de brilho com NAD+ e PDRN 150 ml</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>133.9</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ PDRN Glow Boosting Toner</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" s="4" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-nad-pdrn-glow-boosting-toner</t>
+        </is>
+      </c>
+      <c r="L49" s="2">
+        <f>ROUND(H49*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M49" s="6">
+        <f>IF(OR(D49="",L49=""),"",D49/L49-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MB000955</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ Retinal Volumetox Eye Cream: creme para olhos com retinal e NAD+ 20 ml</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>127.9</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ Retinal Volumetox Eye Cream</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" s="4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-nad-retinal-volumetox-eye-cream</t>
+        </is>
+      </c>
+      <c r="L50" s="2">
+        <f>ROUND(H50*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M50" s="6">
+        <f>IF(OR(D50="",L50=""),"",D50/L50-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MB000954</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ Retinol Volumetox Eye Cream: creme para olhos com retinol e NAD+ 10 ml</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ Retinol Volumetox Eye Cream</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-nad-retinol-volumetox-eye-cream</t>
+        </is>
+      </c>
+      <c r="L51" s="2">
+        <f>ROUND(H51*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M51" s="6">
+        <f>IF(OR(D51="",L51=""),"",D51/L51-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MB000952</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pore Tightening Routine Set: óleo + espuma de limpeza + sérum de retinol para poros</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Pore Tightening Routine Set</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" s="4" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/pore-tightening-routine-set</t>
+        </is>
+      </c>
+      <c r="L52" s="2">
+        <f>ROUND(H52*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M52" s="6">
+        <f>IF(OR(D52="",L52=""),"",D52/L52-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MB000951</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Special Eye Treatment Set: creme para olhos No.9 com retinol + 10 pares de adesivos</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>310.9</v>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Certeiro</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Special Eye Treatment Set</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" s="4" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/special-eye-treatment-set</t>
+        </is>
+      </c>
+      <c r="L53" s="2">
+        <f>ROUND(H53*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M53" s="6">
+        <f>IF(OR(D53="",L53=""),"",D53/L53-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MB000997</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>No.2 Rose PDRN Collagen Plumping Serum: sérum de colágeno e PDRN de rosa 30 ml</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>No.2 Rose PDRN Collagen 2X Plumping Serum</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" s="4" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-2-rose-pdrn-collagen-2x-plumping-serum</t>
+        </is>
+      </c>
+      <c r="L54" s="2">
+        <f>ROUND(H54*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M54" s="6">
+        <f>IF(OR(D54="",L54=""),"",D54/L54-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MB000988</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>No.3 Pore Care 3 Step Routine Set: tônico + sérum + máscara para poros</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>337.9</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>No.3 Pore Care 3 Step Routine Set</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" s="4" t="n">
+        <v>46.36</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-pore-care-3-step-routine-set-2</t>
+        </is>
+      </c>
+      <c r="L55" s="2">
+        <f>ROUND(H55*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M55" s="6">
+        <f>IF(OR(D55="",L55=""),"",D55/L55-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MB000985</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>No.3 Skin Softening Serum: sérum de fermentados para poros e textura 50 ml</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>No.3 Skin Softening Serum</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-3-skin-softening-serum-1</t>
+        </is>
+      </c>
+      <c r="L56" s="2">
+        <f>ROUND(H56*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M56" s="6">
+        <f>IF(OR(D56="",L56=""),"",D56/L56-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MB000976</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>No.5 Glutathione TXA Advanced: ampola concentrada para a aparência de manchas 10 g</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>179.9</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>No.5 Glutathione TXA Advanced Dark Spot Ampoule Concentrate</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0.35 fl.oz. / 10g</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-5-glutathione-txa-advanced-dark-spot-ampoule-concentrate</t>
+        </is>
+      </c>
+      <c r="L57" s="2">
+        <f>ROUND(H57*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M57" s="6">
+        <f>IF(OR(D57="",L57=""),"",D57/L57-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MB000963</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>No.9 Lifting Duo: essência firmadora + máscara com faixa de lifting</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>319.9</v>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>No.9 Lifting Duo</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-lifting-duo</t>
+        </is>
+      </c>
+      <c r="L58" s="2">
+        <f>ROUND(H58*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M58" s="6">
+        <f>IF(OR(D58="",L58=""),"",D58/L58-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MB000962</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>No.9 Lifting Special Set: essência + creme para olhos com retinol + adesivos</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>392.9</v>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>No.9 Lifting Special Set</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-lifting-special-set</t>
+        </is>
+      </c>
+      <c r="L59" s="2">
+        <f>ROUND(H59*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M59" s="6">
+        <f>IF(OR(D59="",L59=""),"",D59/L59-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MB000965</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ BIO Lifting-sil Full Face Mask: kit com 16 máscaras + 4 faixas</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>448.9</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>No.9  NAD+ BIO Face Mask Bundle (16 Sheets + 4 Lifting Bands)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" s="4" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="I60" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-nad-bio-lifting-sil-full-face-mask-bundle-16-sheets-4-lifting-bands</t>
+        </is>
+      </c>
+      <c r="L60" s="2">
+        <f>ROUND(H60*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M60" s="6">
+        <f>IF(OR(D60="",L60=""),"",D60/L60-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MB000958</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ Early 20s Set: essência firmadora + creme para olhos com retinal</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>316.9</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ Early 20s Anti-Aging Set</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" s="4" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-nad-daily-glow-basic-duo</t>
+        </is>
+      </c>
+      <c r="L61" s="2">
+        <f>ROUND(H61*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M61" s="6">
+        <f>IF(OR(D61="",L61=""),"",D61/L61-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MB000953</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>No.9 Ultimate Lifting Set: rotina firmadora com NAD+ em 5 itens</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>608.9</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>No.9 Ultimate Lifting Set (5 Items)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" s="4" t="n">
+        <v>83.52</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-ultimate-lifting-set-1</t>
+        </is>
+      </c>
+      <c r="L62" s="2">
+        <f>ROUND(H62*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M62" s="6">
+        <f>IF(OR(D62="",L62=""),"",D62/L62-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MB001014</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Cool Down Eye Ritual: 2 cremes para olhos No.9 (retinal e retinol) + adesivos</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Cool Down Eye Ritual</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/cool-down-eye-ritual</t>
+        </is>
+      </c>
+      <c r="L63" s="2">
+        <f>ROUND(H63*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M63" s="6">
+        <f>IF(OR(D63="",L63=""),"",D63/L63-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MB000995</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>No.2 Rose PDRN Overnight Collagen Mask: máscara noturna de colágeno, 4 unidades</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>No.2 Rose PDRN Overnight Collagen Mask (4 Masks)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-2-rose-pdrn-overnight-collagen-mask</t>
+        </is>
+      </c>
+      <c r="L64" s="2">
+        <f>ROUND(H64*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M64" s="6">
+        <f>IF(OR(D64="",L64=""),"",D64/L64-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MB000960</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ BIO Lifting-sil Full Face Mask: máscara firmadora, 4 unidades + faixa</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ BIO Lifting-sil Full Face Mask</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" s="4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-nad-bio-lifting-sil-full-face-mask</t>
+        </is>
+      </c>
+      <c r="L65" s="2">
+        <f>ROUND(H65*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M65" s="6">
+        <f>IF(OR(D65="",L65=""),"",D65/L65-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MB000950</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>The Advanced Glow Ritual: kit No.9 com NAD+ em 6 itens</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>718.9</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Conferir (tamanho/kit diferente)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>The Advanced Glow Ritual (6 items)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/the-advanced-glow-ritual-set-6-items</t>
+        </is>
+      </c>
+      <c r="L66" s="2">
+        <f>ROUND(H66*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M66" s="6">
+        <f>IF(OR(D66="",L66=""),"",D66/L66-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MB003179</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2 Sérum de Colágeno PDRN 2X Rosa 30ml</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>No.2 Rose PDRN Collagen 2X Plumping Serum</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" s="4" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-2-rose-pdrn-collagen-2x-plumping-serum</t>
+        </is>
+      </c>
+      <c r="L67" s="2">
+        <f>ROUND(H67*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M67" s="6">
+        <f>IF(OR(D67="",L67=""),"",D67/L67-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MB003182</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deep Cleansing Creamy Facial Foam #2, 120ml</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>No.2 Deep Clean Fresh Cream Cleansing Foam</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-2-deep-clean-fresh-cream-cleansing-foam</t>
+        </is>
+      </c>
+      <c r="L68" s="2">
+        <f>ROUND(H68*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M68" s="6">
+        <f>IF(OR(D68="",L68=""),"",D68/L68-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MB003180</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Sérum para Máscara Facial No. 6 Deep Sleep 50ml</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>No.6 Deep Sleep Mask Serum</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-6-deep-sleep-mask-serum-1</t>
+        </is>
+      </c>
+      <c r="L69" s="2">
+        <f>ROUND(H69*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M69" s="6">
+        <f>IF(OR(D69="",L69=""),"",D69/L69-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MB003189</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1 Almofadas de Cica Calmantes – 70 Almofadas</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>67.89</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="n"/>
+      <c r="I70" s="4" t="n"/>
+      <c r="L70" s="2" t="n"/>
+      <c r="M70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MB003174</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1 Discos Calmantes de Cica – 70 Discos</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>67.89</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="n"/>
+      <c r="I71" s="4" t="n"/>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MB003176</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2 Sérum Preenchedor com PDRN de Rosa e Colágeno – 30 ml</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>141.9</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MB003177</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>3 Ampola Remodeladora de Poros com Biorretinol Azul – 30 ml</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>153.9</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="n"/>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MB003175</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>4 Sérum Ceraphyl Efeito "Pele de Ovo" – 30 ml</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>78.33</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="n"/>
+      <c r="L74" s="2" t="n"/>
+      <c r="M74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MB003171</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5 Adesivos de Glutationa C para Marcas e Manchas – 70 Unidades</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>68.23999999999999</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="L75" s="2" t="n"/>
+      <c r="M75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MB003192</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5 Ampoules Glutathione C for Marks and Spots – 30 ml</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n"/>
+      <c r="L76" s="2" t="n"/>
+      <c r="M76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MB003190</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5 Máscara Facial em Filme com Glutationa e Vitamina C – 5 Unidades</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="n"/>
+      <c r="I77" s="4" t="n"/>
+      <c r="L77" s="2" t="n"/>
+      <c r="M77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MB001017</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Cofre de Skincare Brilho 24/7 (7 itens)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>752.9</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="n"/>
+      <c r="I78" s="4" t="n"/>
+      <c r="L78" s="2" t="n"/>
+      <c r="M78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MB003193</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Discos de Tônico, 2 tipos, 1+1 (140 discos)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="n"/>
+      <c r="I79" s="4" t="n"/>
+      <c r="L79" s="2" t="n"/>
+      <c r="M79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MB003181</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Essential Tonic Vita-Glutathione C Supplement No. 5 200ml</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="n"/>
+      <c r="I80" s="4" t="n"/>
+      <c r="L80" s="2" t="n"/>
+      <c r="M80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MB003194</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Kit de Máscaras 1+1, 6 tipos (10 unidades)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>214.9</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="n"/>
+      <c r="I81" s="4" t="n"/>
+      <c r="L81" s="2" t="n"/>
+      <c r="M81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MB003178</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Máscara Facial de Colágeno PDRN Rosa nº 2 (5 unidades)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n"/>
+      <c r="I82" s="4" t="n"/>
+      <c r="L82" s="2" t="n"/>
+      <c r="M82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MB003172</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>No.3 PHA Prep Bubble Pack: espuma de bolhas com PHA para textura 90 ml</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>144.9</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="n"/>
+      <c r="I83" s="4" t="n"/>
+      <c r="L83" s="2" t="n"/>
+      <c r="M83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MB003173</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Pads de Maquiagem Sem Poros nº 3 - 70 unidades</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>81.47</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="n"/>
+      <c r="I84" s="4" t="n"/>
+      <c r="L84" s="2" t="n"/>
+      <c r="M84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MB001013</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ritual Refrescante para os Olhos (3 unidades)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>768.9</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="n"/>
+      <c r="I85" s="4" t="n"/>
+      <c r="L85" s="2" t="n"/>
+      <c r="M85" s="6" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MB003220</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Shampoo Sérum Perfect Magic Straight 530 ml</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>44.92</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="n"/>
+      <c r="I86" s="4" t="n"/>
+      <c r="L86" s="2" t="n"/>
+      <c r="M86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>MB000975</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sérum No.5 para a aparência de manchas</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>188.9</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="n"/>
+      <c r="I87" s="4" t="n"/>
+      <c r="L87" s="2" t="n"/>
+      <c r="M87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>MB003185</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Tônico Calmante e Purificante para Pele Clara – 300 ml</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>137.9</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="n"/>
+      <c r="I88" s="4" t="n"/>
+      <c r="L88" s="2" t="n"/>
+      <c r="M88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>MB003188</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tônico Intensificador para Preparação da Pele – 200 ml</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="n"/>
+      <c r="I89" s="4" t="n"/>
+      <c r="L89" s="2" t="n"/>
+      <c r="M89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>MB003187</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tônico de Tratamento Glow com NMN e PDRN – 150 ml</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="n"/>
+      <c r="I90" s="4" t="n"/>
+      <c r="L90" s="2" t="n"/>
+      <c r="M90" s="6" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>MB003191</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>numbuzin No.1 Cheongcho FPS 50+ PA++++: dupla de protetor solar calmante 2 x 50 ml</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>279.9</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="n"/>
+      <c r="I91" s="4" t="n"/>
+      <c r="L91" s="2" t="n"/>
+      <c r="M91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MB003184</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>numbuzin No.1 Cheongcho FPS 50+ PA++++: protetor solar calmante com filme de água 50 ml</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="n"/>
+      <c r="I92" s="4" t="n"/>
+      <c r="L92" s="2" t="n"/>
+      <c r="M92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>MB003183</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>numbuzin No.3 Porcelana Tone-up Beige FPS 50+ PA++++: protetor solar com cor 50 ml</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>139.9</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Sem par</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="n"/>
+      <c r="L93" s="2" t="n"/>
+      <c r="M93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
           <t>MB003186</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>Óleo de Limpeza Suave para Poros Nº 3 200ml</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
         <v>151.9</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>Sem par</t>
         </is>
       </c>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="6" t="n"/>
+      <c r="H94" s="4" t="n"/>
+      <c r="I94" s="4" t="n"/>
+      <c r="L94" s="2" t="n"/>
+      <c r="M94" s="6" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1655,10 +5034,70 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId69"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4312,7 +7751,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://numbuzinus.com · loja "numbuzin" · moeda USD · lido em 30/10/2026 06:04 UTC</t>
+          <t>Site oficial: https://numbuzinus.com · loja "numbuzin" · moeda USD · lido em 30/10/2026 06:05 UTC</t>
         </is>
       </c>
     </row>

--- a/tools/precos/planilhas/precos-oficiais-numbuzin.xlsx
+++ b/tools/precos/planilhas/precos-oficiais-numbuzin.xlsx
@@ -3917,12 +3917,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MB001014</t>
+          <t>MB003180</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cool Down Eye Ritual: 2 cremes para olhos No.9 (retinal e retinol) + adesivos</t>
+          <t>Sérum para Máscara Facial No. 6 Deep Sleep 50ml</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3931,24 +3931,24 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>279.9</v>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>Conferir (tamanho/kit diferente)</t>
+        <v>152.9</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>Provável — conferir</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cool Down Eye Ritual</t>
+          <t>No.6 Deep Sleep Mask Serum</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="4" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/cool-down-eye-ritual</t>
+          <t>https://numbuzinus.com/products/no-6-deep-sleep-mask-serum-1</t>
         </is>
       </c>
       <c r="L63" s="2">
@@ -3972,12 +3972,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MB000995</t>
+          <t>MB001014</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>No.2 Rose PDRN Overnight Collagen Mask: máscara noturna de colágeno, 4 unidades</t>
+          <t>Cool Down Eye Ritual: 2 cremes para olhos No.9 (retinal e retinol) + adesivos</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>279.9</v>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
@@ -3995,15 +3995,15 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>No.2 Rose PDRN Overnight Collagen Mask (4 Masks)</t>
+          <t>Cool Down Eye Ritual</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="4" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-2-rose-pdrn-overnight-collagen-mask</t>
+          <t>https://numbuzinus.com/products/cool-down-eye-ritual</t>
         </is>
       </c>
       <c r="L64" s="2">
@@ -4027,12 +4027,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MB000960</t>
+          <t>MB003178</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>No.9 NAD+ BIO Lifting-sil Full Face Mask: máscara firmadora, 4 unidades + faixa</t>
+          <t>Máscara Facial de Colágeno PDRN Rosa nº 2 (5 unidades)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>159.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>No.9 NAD+ BIO Lifting-sil Full Face Mask</t>
+          <t>No.2 Rose PDRN Overnight Collagen Mask (4 Masks)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="4" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="I65" s="4" t="n">
         <v>22</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-9-nad-bio-lifting-sil-full-face-mask</t>
+          <t>https://numbuzinus.com/products/no-2-rose-pdrn-overnight-collagen-mask</t>
         </is>
       </c>
       <c r="L65" s="2">
@@ -4082,12 +4082,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>MB000950</t>
+          <t>MB000995</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Advanced Glow Ritual: kit No.9 com NAD+ em 6 itens</t>
+          <t>No.2 Rose PDRN Overnight Collagen Mask: máscara noturna de colágeno, 4 unidades</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>718.9</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
@@ -4105,15 +4105,15 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>The Advanced Glow Ritual (6 items)</t>
+          <t>No.2 Rose PDRN Overnight Collagen Mask (4 Masks)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="4" t="n">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>141</v>
+        <v>22</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/the-advanced-glow-ritual-set-6-items</t>
+          <t>https://numbuzinus.com/products/no-2-rose-pdrn-overnight-collagen-mask</t>
         </is>
       </c>
       <c r="L66" s="2">
@@ -4137,12 +4137,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>MB003179</t>
+          <t>MB000960</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2 Sérum de Colágeno PDRN 2X Rosa 30ml</t>
+          <t>No.9 NAD+ BIO Lifting-sil Full Face Mask: máscara firmadora, 4 unidades + faixa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4151,24 +4151,24 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>152.9</v>
+        <v>159.9</v>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>No.2 Rose PDRN Collagen 2X Plumping Serum</t>
+          <t>No.9 NAD+ BIO Lifting-sil Full Face Mask</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="4" t="n">
-        <v>19.6</v>
+        <v>16.5</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-2-rose-pdrn-collagen-2x-plumping-serum</t>
+          <t>https://numbuzinus.com/products/no-9-nad-bio-lifting-sil-full-face-mask</t>
         </is>
       </c>
       <c r="L67" s="2">
@@ -4192,12 +4192,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>MB003182</t>
+          <t>MB001013</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deep Cleansing Creamy Facial Foam #2, 120ml</t>
+          <t>Ritual Refrescante para os Olhos (3 unidades)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4206,24 +4206,24 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>80.90000000000001</v>
+        <v>768.9</v>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>No.2 Deep Clean Fresh Cream Cleansing Foam</t>
+          <t>Cool Down Eye Ritual</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="4" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="I68" s="4" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-2-deep-clean-fresh-cream-cleansing-foam</t>
+          <t>https://numbuzinus.com/products/cool-down-eye-ritual</t>
         </is>
       </c>
       <c r="L68" s="2">
@@ -4247,12 +4247,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>MB003180</t>
+          <t>MB000950</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Sérum para Máscara Facial No. 6 Deep Sleep 50ml</t>
+          <t>The Advanced Glow Ritual: kit No.9 com NAD+ em 6 itens</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4261,24 +4261,24 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>152.9</v>
+        <v>718.9</v>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Fraco — conferir</t>
+          <t>Conferir (tamanho/kit diferente)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>No.6 Deep Sleep Mask Serum</t>
+          <t>The Advanced Glow Ritual (6 items)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="4" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I69" s="4" t="n">
-        <v>28</v>
+        <v>141</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>https://numbuzinus.com/products/no-6-deep-sleep-mask-serum-1</t>
+          <t>https://numbuzinus.com/products/the-advanced-glow-ritual-set-6-items</t>
         </is>
       </c>
       <c r="L69" s="2">
@@ -4302,12 +4302,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>MB003189</t>
+          <t>MB003176</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1 Almofadas de Cica Calmantes – 70 Almofadas</t>
+          <t>2 Sérum Preenchedor com PDRN de Rosa e Colágeno – 30 ml</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4316,27 +4316,53 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>67.89</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="n"/>
-      <c r="L70" s="2" t="n"/>
-      <c r="M70" s="6" t="n"/>
+        <v>141.9</v>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>No.2 Rose PDRN Collagen 2X Plumping Serum</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" s="4" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-2-rose-pdrn-collagen-2x-plumping-serum</t>
+        </is>
+      </c>
+      <c r="L70" s="2">
+        <f>ROUND(H70*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M70" s="6">
+        <f>IF(OR(D70="",L70=""),"",D70/L70-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>MB003174</t>
+          <t>MB003179</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1 Discos Calmantes de Cica – 70 Discos</t>
+          <t>2 Sérum de Colágeno PDRN 2X Rosa 30ml</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4345,27 +4371,53 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>67.89</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
-      <c r="L71" s="2" t="n"/>
-      <c r="M71" s="6" t="n"/>
+        <v>152.9</v>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>No.2 Rose PDRN Collagen 2X Plumping Serum</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" s="4" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-2-rose-pdrn-collagen-2x-plumping-serum</t>
+        </is>
+      </c>
+      <c r="L71" s="2">
+        <f>ROUND(H71*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M71" s="6">
+        <f>IF(OR(D71="",L71=""),"",D71/L71-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MB003176</t>
+          <t>MB003182</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2 Sérum Preenchedor com PDRN de Rosa e Colágeno – 30 ml</t>
+          <t>Deep Cleansing Creamy Facial Foam #2, 120ml</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4374,27 +4426,53 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>141.9</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="n"/>
-      <c r="L72" s="2" t="n"/>
-      <c r="M72" s="6" t="n"/>
+        <v>80.90000000000001</v>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>No.2 Deep Clean Fresh Cream Cleansing Foam</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-2-deep-clean-fresh-cream-cleansing-foam</t>
+        </is>
+      </c>
+      <c r="L72" s="2">
+        <f>ROUND(H72*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M72" s="6">
+        <f>IF(OR(D72="",L72=""),"",D72/L72-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MB003177</t>
+          <t>MB003187</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3 Ampola Remodeladora de Poros com Biorretinol Azul – 30 ml</t>
+          <t>Tônico de Tratamento Glow com NMN e PDRN – 150 ml</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4403,27 +4481,53 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>153.9</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Sem par</t>
-        </is>
-      </c>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
-      <c r="L73" s="2" t="n"/>
-      <c r="M73" s="6" t="n"/>
+        <v>123.9</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>Fraco — conferir</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>No.9 NAD+ PDRN Glow Boosting Toner</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" s="4" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>https://numbuzinus.com/products/no-9-nad-pdrn-glow-boosting-toner</t>
+        </is>
+      </c>
+      <c r="L73" s="2">
+        <f>ROUND(H73*(1+Parâmetros!$B$2)*Parâmetros!$B$1,2)</f>
+        <v/>
+      </c>
+      <c r="M73" s="6">
+        <f>IF(OR(D73="",L73=""),"",D73/L73-1)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MB003175</t>
+          <t>MB003189</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4 Sérum Ceraphyl Efeito "Pele de Ovo" – 30 ml</t>
+          <t>1 Almofadas de Cica Calmantes – 70 Almofadas</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4432,7 +4536,7 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>78.33</v>
+        <v>67.89</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -4447,12 +4551,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>MB003171</t>
+          <t>MB003174</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5 Adesivos de Glutationa C para Marcas e Manchas – 70 Unidades</t>
+          <t>1 Discos Calmantes de Cica – 70 Discos</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4461,7 +4565,7 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>68.23999999999999</v>
+        <v>67.89</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -4476,12 +4580,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MB003192</t>
+          <t>MB003177</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5 Ampoules Glutathione C for Marks and Spots – 30 ml</t>
+          <t>3 Ampola Remodeladora de Poros com Biorretinol Azul – 30 ml</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4490,7 +4594,7 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>73.11</v>
+        <v>153.9</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -4505,12 +4609,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MB003190</t>
+          <t>MB003175</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5 Máscara Facial em Filme com Glutationa e Vitamina C – 5 Unidades</t>
+          <t>4 Sérum Ceraphyl Efeito "Pele de Ovo" – 30 ml</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4519,7 +4623,7 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>109.9</v>
+        <v>78.33</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -4534,12 +4638,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MB001017</t>
+          <t>MB003171</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cofre de Skincare Brilho 24/7 (7 itens)</t>
+          <t>5 Adesivos de Glutationa C para Marcas e Manchas – 70 Unidades</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4548,7 +4652,7 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>752.9</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -4563,12 +4667,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>MB003193</t>
+          <t>MB003192</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Discos de Tônico, 2 tipos, 1+1 (140 discos)</t>
+          <t>5 Ampoules Glutathione C for Marks and Spots – 30 ml</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4577,7 +4681,7 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>279.9</v>
+        <v>73.11</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4592,12 +4696,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MB003181</t>
+          <t>MB003190</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Essential Tonic Vita-Glutathione C Supplement No. 5 200ml</t>
+          <t>5 Máscara Facial em Filme com Glutationa e Vitamina C – 5 Unidades</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4606,7 +4710,7 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>62.67</v>
+        <v>109.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4621,12 +4725,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MB003194</t>
+          <t>MB001017</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Kit de Máscaras 1+1, 6 tipos (10 unidades)</t>
+          <t>Cofre de Skincare Brilho 24/7 (7 itens)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4635,7 +4739,7 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>214.9</v>
+        <v>752.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -4650,12 +4754,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MB003178</t>
+          <t>MB003193</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Máscara Facial de Colágeno PDRN Rosa nº 2 (5 unidades)</t>
+          <t>Discos de Tônico, 2 tipos, 1+1 (140 discos)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4664,7 +4768,7 @@
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>86.90000000000001</v>
+        <v>279.9</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4679,12 +4783,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MB003172</t>
+          <t>MB003181</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>No.3 PHA Prep Bubble Pack: espuma de bolhas com PHA para textura 90 ml</t>
+          <t>Essential Tonic Vita-Glutathione C Supplement No. 5 200ml</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4693,7 +4797,7 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>144.9</v>
+        <v>62.67</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4708,12 +4812,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MB003173</t>
+          <t>MB003194</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pads de Maquiagem Sem Poros nº 3 - 70 unidades</t>
+          <t>Kit de Máscaras 1+1, 6 tipos (10 unidades)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4722,7 +4826,7 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>81.47</v>
+        <v>214.9</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4737,12 +4841,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MB001013</t>
+          <t>MB003172</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ritual Refrescante para os Olhos (3 unidades)</t>
+          <t>No.3 PHA Prep Bubble Pack: espuma de bolhas com PHA para textura 90 ml</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4751,7 +4855,7 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>768.9</v>
+        <v>144.9</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4766,12 +4870,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MB003220</t>
+          <t>MB003173</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Shampoo Sérum Perfect Magic Straight 530 ml</t>
+          <t>Pads de Maquiagem Sem Poros nº 3 - 70 unidades</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4780,7 +4884,7 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>44.92</v>
+        <v>81.47</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4795,12 +4899,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MB000975</t>
+          <t>MB003220</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sérum No.5 para a aparência de manchas</t>
+          <t>Shampoo Sérum Perfect Magic Straight 530 ml</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4809,7 +4913,7 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>188.9</v>
+        <v>44.92</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4824,12 +4928,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MB003185</t>
+          <t>MB000975</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tônico Calmante e Purificante para Pele Clara – 300 ml</t>
+          <t>Sérum No.5 para a aparência de manchas</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4838,7 +4942,7 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>137.9</v>
+        <v>188.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4853,12 +4957,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MB003188</t>
+          <t>MB003185</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tônico Intensificador para Preparação da Pele – 200 ml</t>
+          <t>Tônico Calmante e Purificante para Pele Clara – 300 ml</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4867,7 +4971,7 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>120.9</v>
+        <v>137.9</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4882,12 +4986,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MB003187</t>
+          <t>MB003188</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tônico de Tratamento Glow com NMN e PDRN – 150 ml</t>
+          <t>Tônico Intensificador para Preparação da Pele – 200 ml</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4896,7 +5000,7 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>123.9</v>
+        <v>120.9</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -5094,10 +5198,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K73" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId69"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId73"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7751,7 +7859,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site oficial: https://numbuzinus.com · loja "numbuzin" · moeda USD · lido em 30/10/2026 06:05 UTC</t>
+          <t>Site oficial: https://numbuzinus.com · loja "numbuzin" · moeda USD · lido em 30/10/2026 06:07 UTC</t>
         </is>
       </c>
     </row>
